--- a/marketing_surveys/042_novel_search_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/042_novel_search_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>award_winning</t>
+          <t>award winning</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mystery_novels</t>
+          <t>mystery novels</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>science_fiction</t>
+          <t>science fiction</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>time_travel</t>
+          <t>time travel</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>urban_fantasy</t>
+          <t>urban fantasy</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
